--- a/DSA.xlsx
+++ b/DSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026\learninglog\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82414212-B978-4B9C-9A31-A2A6C49AE4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9F48BD-61B5-4780-8D52-BAE67E9BC757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,16 @@
     <sheet name="Recurrsion" sheetId="3" r:id="rId3"/>
     <sheet name="Tree" sheetId="4" r:id="rId4"/>
     <sheet name="Graph" sheetId="5" r:id="rId5"/>
-    <sheet name="LinkedList" sheetId="6" r:id="rId6"/>
-    <sheet name="Subarray" sheetId="8" r:id="rId7"/>
-    <sheet name="Sliding Window" sheetId="7" r:id="rId8"/>
+    <sheet name="Bitmanupulation" sheetId="9" r:id="rId6"/>
+    <sheet name="LinkedList" sheetId="6" r:id="rId7"/>
+    <sheet name="Subarray" sheetId="8" r:id="rId8"/>
+    <sheet name="Sliding Window" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Graph!$A$1:$N$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Sliding Window'!$A$1:$O$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Subarray!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Bitmanupulation!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Graph!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Sliding Window'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Subarray!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="254">
   <si>
     <t xml:space="preserve">Problem Name </t>
   </si>
@@ -1639,9 +1641,6 @@
       </rPr>
       <t>No need to use visited array to prevent mutiple updates for already visited cell . we can use distance from that as well .</t>
     </r>
-  </si>
-  <si>
-    <t>#1</t>
   </si>
   <si>
     <t>Revision (#1-26-01-25)</t>
@@ -2011,73 +2010,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">NEED : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Dijkstra don't work on negative edges and gives tle in case of negative cycle in the graph . 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>APPROCH :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 
-- Intialize the cost with MAX except Source node .
-- Iterate over the edges totalnodes-1 times and update cost array for the node if we can reach it with minimum cost than previous.
-- while Iterating on edges Nth time if we find any updation then return saying "Cycle exists in the graph".
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>NOTES :</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cycle in a graph which contain at least one negative edge doesn't means negative cycle . Sum of the cycle path must be less than zero to say "Negative Cycle".</t>
-    </r>
-  </si>
-  <si>
     <t>https://takeuforward.org/data-structure/floyd-warshall-algorithm-g-42</t>
   </si>
   <si>
@@ -2207,12 +2139,171 @@
     <t>TC - O(n^3)
 SC - O(n)</t>
   </si>
+  <si>
+    <t>696. Count Binary Substrings</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/count-binary-substrings</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/count-binary-substrings/solutions/7590577/count-binary-substrings-easy-solution-by-it1w/?envType=daily-question&amp;envId=2026-02-19</t>
+  </si>
+  <si>
+    <t>TC - O(n)</t>
+  </si>
+  <si>
+    <t>Bitmanupulation</t>
+  </si>
+  <si>
+    <t>POTD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">NEED : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Dijkstra don't work on negative edges and gives tle in case of negative cycle in the graph . 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>APPROCH :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+- Intialize the cost with MAX except Source node .
+- Iterate over the edges totalnodes-1 times and update cost array for the node if we can reach it with minimum cost than previous.
+- while Iterating on edges Nth time if we find any updation then return saying "Negative Cycle exists in the graph".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOTES :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cycle in a graph which contain at least one negative edge doesn't means negative cycle . Sum of the cycle path must be less than zero to say "Negative Cycle".</t>
+    </r>
+  </si>
+  <si>
+    <t>#1-09-03-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>#1-11-03-26</t>
+  </si>
+  <si>
+    <t>MST - Prims Algo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC - O(E log V) </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NEED :  To find minimum spanning tree . 
+Maintain a sum variable and list to maintain Min. sum and pair of the mst.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Algorithum :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+1. Initialize the visited array and priority queue - (weight,node,parent).
+2. Add any node as starting node with (0,node ,-1).
+3. while q is not empty 
+3.1 poll the peek of pq , if it's not already been visited, mark it as visited .
+3.2 explore its adjacent , if adjancent is not visited  and add in the queue .
+4 repeat </t>
+    </r>
+  </si>
+  <si>
+    <t>1584. Min Cost to Connect All Points</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/min-cost-to-connect-all-points/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intution : If we represent (x,y) as vertex , then problem comes down to MST by prims . 
+Hint : As all  (x,y) are unique we can consider points.length == no. vertexs and we will calculate distance between them as weight . 
+Approch : represent each (x,y) vertex and create adjacency list with everyother vertex . </t>
+  </si>
+  <si>
+    <t>TC - O(n^2 log n)</t>
+  </si>
+  <si>
+    <t>MST Prim's algo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disjoint Set By Rank and Size </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2266,6 +2357,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2971,7 +3069,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627F4D11-A7C4-43BB-9B31-F105D2E4CA7B}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.90625" style="5" customWidth="1"/>
@@ -3014,7 +3112,7 @@
         <v>140</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>44</v>
@@ -3058,7 +3156,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>77</v>
@@ -3096,7 +3194,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>80</v>
@@ -3131,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>79</v>
@@ -3166,7 +3264,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>49</v>
@@ -3201,7 +3299,7 @@
         <v>5</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>49</v>
@@ -3236,7 +3334,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>84</v>
@@ -3256,7 +3354,7 @@
         <v>62</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>82</v>
@@ -3667,7 +3765,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>32</v>
@@ -3757,7 +3855,7 @@
         <v>179</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>32</v>
@@ -3875,7 +3973,7 @@
       <c r="A27" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>191</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -3897,7 +3995,7 @@
         <v>4</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>32</v>
@@ -3911,22 +4009,22 @@
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>194</v>
@@ -3934,6 +4032,9 @@
       <c r="H28" s="5">
         <v>3</v>
       </c>
+      <c r="I28" s="5" t="s">
+        <v>240</v>
+      </c>
       <c r="K28" s="9" t="s">
         <v>32</v>
       </c>
@@ -3946,16 +4047,16 @@
     </row>
     <row r="29" spans="1:13" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>25</v>
@@ -3964,27 +4065,30 @@
         <v>66</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H29" s="5">
         <v>4</v>
       </c>
+      <c r="I29" s="5" t="s">
+        <v>241</v>
+      </c>
       <c r="J29" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>32</v>
@@ -3996,21 +4100,21 @@
         <v>3</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="261" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>25</v>
@@ -4019,17 +4123,80 @@
         <v>43</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H31" s="5">
         <v>4</v>
       </c>
+      <c r="I31" s="5" t="s">
+        <v>240</v>
+      </c>
       <c r="M31" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="H32" s="5">
+        <v>3</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H33" s="5">
+        <v>3</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N27" xr:uid="{627F4D11-A7C4-43BB-9B31-F105D2E4CA7B}"/>
+  <autoFilter ref="A1:N32" xr:uid="{627F4D11-A7C4-43BB-9B31-F105D2E4CA7B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" display="https://takeuforward.org/plus/dsa/problems/connected-components" xr:uid="{CBDDA4D9-3DA6-42F4-BD81-6766CE6059E4}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{D4ED72D4-0FD6-484E-AD61-CDBC7D2FE01F}"/>
@@ -4052,13 +4219,119 @@
     <hyperlink ref="B28" r:id="rId19" xr:uid="{5CEB0A28-62E3-4F7D-9DA7-371B1C990640}"/>
     <hyperlink ref="B29" r:id="rId20" xr:uid="{ED6D3629-9BAC-4F79-9135-D4EA70CC2E96}"/>
     <hyperlink ref="B30" r:id="rId21" xr:uid="{6A758F7A-79FB-495C-B418-9EDF46598B5E}"/>
+    <hyperlink ref="B31" r:id="rId22" xr:uid="{3472C449-0813-4249-A912-7371C1132D75}"/>
+    <hyperlink ref="B27" r:id="rId23" xr:uid="{E7B363CE-2ADD-4EB8-BDCC-4504C7B2FC63}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId22"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD994AD9-DD9F-4AD2-9BE6-CF2C5785A85E}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.08984375" style="2" customWidth="1"/>
+    <col min="2" max="3" width="26.1796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.90625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" style="2"/>
+    <col min="9" max="9" width="17.08984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.6328125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.81640625" style="2" customWidth="1"/>
+    <col min="13" max="14" width="17.453125" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H2" s="2">
+        <v>3</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1" xr:uid="{AD994AD9-DD9F-4AD2-9BE6-CF2C5785A85E}"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{A2DE0EB7-AD60-4324-8920-12328C3E6B73}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{09E9CC2E-6823-446F-944E-E57BE9EFB526}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D90093C-235B-4BFA-AC06-070A87C8F0C6}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4169,7 +4442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C97E19B9-CD82-4865-8D9B-AA4D0F508F84}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4213,7 +4486,7 @@
         <v>140</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>44</v>
@@ -4233,37 +4506,37 @@
     </row>
     <row r="2" spans="1:14" s="9" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>218</v>
-      </c>
       <c r="C2" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H2" s="9">
         <v>3</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E5" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4275,7 +4548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBB5AD9-6759-49B8-8C85-DCC62C1F65FC}">
   <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4321,7 +4594,7 @@
         <v>140</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>44</v>
@@ -4341,16 +4614,16 @@
     </row>
     <row r="2" spans="1:14" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>25</v>
@@ -4359,33 +4632,33 @@
         <v>43</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H2" s="5">
         <v>3</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B3" s="7"/>
       <c r="L3" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="9" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>25</v>
@@ -4394,16 +4667,16 @@
         <v>66</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H4" s="9">
         <v>3</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/DSA.xlsx
+++ b/DSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026\learninglog\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9F48BD-61B5-4780-8D52-BAE67E9BC757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631607AA-D6E7-490F-BF7A-3BB84AEC3810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,6 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Subarray!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="264">
   <si>
     <t xml:space="preserve">Problem Name </t>
   </si>
@@ -2296,14 +2297,178 @@
     <t>MST Prim's algo</t>
   </si>
   <si>
-    <t xml:space="preserve">Disjoint Set By Rank and Size </t>
+    <t>https://github.com/satyam-learning-log/DSA/tree/master/DSA_TOPICS/Graph/MinimumSpanningTree_DisjointSetProblems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disjoint Set By Rank and Size - Data structure </t>
+  </si>
+  <si>
+    <t>TC - O(Log N) - for path comparsion but its done only once . 
+Aplha (N) &lt;= 4
+SC - O(N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disjoint Set </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NEED - We can find if vertexes belongs to same component in 0(1) timing at any point of time in dynamic graphs - graphs which keep on changes it size . 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INTUTION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  - If we assign a common representative (parent/root) to all vertices in a connected component,
+then we can determine whether two vertices belong to the same component by checking if they share the same representative.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOTE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - 
+- rank != height - as we do path comparsion we attach child nodes to ultimate parent so it break the rule of calculating the height . 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">APPROCH - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Initialize three arrays:
+  rank[n] = 0  /  size[n] = 1 
+ parent[n] = node it self . 
+- Initially, every node is its own parent, meaning all nodes are separate components.
+- While processing edges:
+  - Find the ULTIMATE PARENT of nodes u and v (pu and pv).
+  - If pu == pv:
+    - They already belong to the same component, so no union is required.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Union by Rank:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  - Attach the component with smaller rank under the component with larger rank.
+  - If both ranks are equal:
+      - Attach one root to the other
+      - Increase the rank of the new root by 1.
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Union by Size:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  - Attach the component with smaller size to the component with larger size.
+  - Update the size of the new root accordingly.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>1319. Number of Operations to Make Network Connected</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/number-of-operations-to-make-network-connected/</t>
+  </si>
+  <si>
+    <t>INTUTIONS: If we can just find number of disconnected components and no.of edges we can  connect disconnected components , with extra edges .
+NOTE : - to connect N vertexes we would need N-1 edges .
+APPROCH : 
+- Process every edge with Disjoint set data structure and fill size / rank and parent array . 
+- After processing if we have more than one distinct ultimate parent then 
+-  check if we have sufficient edges to connect that and return .</t>
+  </si>
+  <si>
+    <t>TC - Aplha (N) &lt;= 4
+SC - O (n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2357,6 +2522,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3069,7 +3242,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627F4D11-A7C4-43BB-9B31-F105D2E4CA7B}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.90625" style="5" customWidth="1"/>
@@ -4190,9 +4363,74 @@
         <v>243</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>253</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H34" s="5">
+        <v>4</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H35" s="5">
+        <v>3</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -4221,9 +4459,10 @@
     <hyperlink ref="B30" r:id="rId21" xr:uid="{6A758F7A-79FB-495C-B418-9EDF46598B5E}"/>
     <hyperlink ref="B31" r:id="rId22" xr:uid="{3472C449-0813-4249-A912-7371C1132D75}"/>
     <hyperlink ref="B27" r:id="rId23" xr:uid="{E7B363CE-2ADD-4EB8-BDCC-4504C7B2FC63}"/>
+    <hyperlink ref="B34" r:id="rId24" xr:uid="{878B70B8-85D8-488D-988D-D9EA1E0D237C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
 
@@ -4247,7 +4486,7 @@
     <col min="15" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>

--- a/DSA.xlsx
+++ b/DSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026\learninglog\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631607AA-D6E7-490F-BF7A-3BB84AEC3810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF39B83-41BE-4954-AF76-DB6D15D14AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="270">
   <si>
     <t xml:space="preserve">Problem Name </t>
   </si>
@@ -2462,6 +2462,41 @@
   </si>
   <si>
     <t xml:space="preserve">No </t>
+  </si>
+  <si>
+    <t>947. Most Stones Removed with Same Row or Column</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/most-stones-removed-with-same-row-or-column</t>
+  </si>
+  <si>
+    <t>Intutions : If we treat each stone’s (row, col) as connected via row or column, stones sharing the same row or column belong to the same component.
+Approch : 
+n^2 - 
+- Treat each coordinate as a vertex.
+- Create edges between vertices having same row or same column.
+- Process edges using Disjoint Set.
+- Count distinct ultimate parents.
+ans = total_vertices − components.
+0(alpha n) 
+- As you would require no of ultimate parents only . 
+- Treat each row as node and column as node.
+- Map column node as:
+- col_node = maxRow + col + 1
+- For each stone (r,c):
+- union(r , maxRow + c + 1).
+- (IMP)Maintain HashSet for nodes involved (It helps us to recognize the dummy row and col which are not vertexs in our graph ).
+- Count distinct ultimate parents among them.
+ - ans = stones − components.</t>
+  </si>
+  <si>
+    <t>TC - O(N · α(N))</t>
+  </si>
+  <si>
+    <t>Medium-hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes - must visit / striver's video </t>
   </si>
 </sst>
 </file>
@@ -3242,7 +3277,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627F4D11-A7C4-43BB-9B31-F105D2E4CA7B}">
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.90625" style="5" customWidth="1"/>
@@ -4430,6 +4465,44 @@
         <v>254</v>
       </c>
       <c r="M35" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H36" s="5">
+        <v>3</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="M36" s="5" t="s">
         <v>254</v>
       </c>
     </row>

--- a/DSA.xlsx
+++ b/DSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026\learninglog\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF39B83-41BE-4954-AF76-DB6D15D14AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBAD9D4-9CC8-4F2A-A828-ABFD3FF1BD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,19 +18,20 @@
     <sheet name="Recurrsion" sheetId="3" r:id="rId3"/>
     <sheet name="Tree" sheetId="4" r:id="rId4"/>
     <sheet name="Graph" sheetId="5" r:id="rId5"/>
-    <sheet name="Bitmanupulation" sheetId="9" r:id="rId6"/>
-    <sheet name="LinkedList" sheetId="6" r:id="rId7"/>
-    <sheet name="Subarray" sheetId="8" r:id="rId8"/>
-    <sheet name="Sliding Window" sheetId="7" r:id="rId9"/>
+    <sheet name="DP" sheetId="10" r:id="rId6"/>
+    <sheet name="Bitmanupulation" sheetId="9" r:id="rId7"/>
+    <sheet name="LinkedList" sheetId="6" r:id="rId8"/>
+    <sheet name="Subarray" sheetId="8" r:id="rId9"/>
+    <sheet name="Sliding Window" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Bitmanupulation!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Bitmanupulation!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DP!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Graph!$A$1:$N$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Sliding Window'!$A$1:$O$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Subarray!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Sliding Window'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Subarray!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="289">
   <si>
     <t xml:space="preserve">Problem Name </t>
   </si>
@@ -2470,11 +2471,20 @@
     <t>https://leetcode.com/problems/most-stones-removed-with-same-row-or-column</t>
   </si>
   <si>
+    <t>TC - O(N · α(N))</t>
+  </si>
+  <si>
+    <t>Medium-hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes - must visit / striver's video </t>
+  </si>
+  <si>
     <t>Intutions : If we treat each stone’s (row, col) as connected via row or column, stones sharing the same row or column belong to the same component.
 Approch : 
 n^2 - 
 - Treat each coordinate as a vertex.
-- Create edges between vertices having same row or same column.
+- "Create edges" between vertices having same row or same column. (n^2)
 - Process edges using Disjoint Set.
 - Count distinct ultimate parents.
 ans = total_vertices − components.
@@ -2490,13 +2500,146 @@
  - ans = stones − components.</t>
   </si>
   <si>
-    <t>TC - O(N · α(N))</t>
-  </si>
-  <si>
-    <t>Medium-hard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes - must visit / striver's video </t>
+    <t>https://leetcode.com/problems/accounts-merge/</t>
+  </si>
+  <si>
+    <t>721. Accounts Merge</t>
+  </si>
+  <si>
+    <t>Intution : If we consider  both person's (indexes) belong to the same component if they have an similar email between them . Then by applying disjoint set we can merge emails easily . 
+Note - Challenge was to find email belongs to which index / collecting indexs based on the email . TC - O(n^2). 
+Approch - 
+- Iterate over all accounts and map each email → index.
+- If an email is already present in the map:
+--Union the current index with the mapped index.
+- After processing all emails, DSU will have formed the components.
+- Create a map: parent → list of emails.
+- For each email:
+-- Find its ultimate parent (account index). (to process all the emails of two different indexes  0 -&gt; j1 , j2 , 1 - j1 , "j5")
+-- Add the email to that parent’s group.
+- Sort emails in each group and return the result.</t>
+  </si>
+  <si>
+    <t>TC -  O(N+E) + O(E*4ɑ) + O(N*(ElogE + E)) where N = no. of indices or nodes and E = no. of emails. The first term is for visiting all the emails. The second term is for merging the accounts. And the third term is for sorting the emails and storing them in the answer array.
+SC - O(N)</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/making-a-large-island/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827. Making A Large Island - 
+Can convert at most one 0-cell to 1-cell . Return largest island can we create </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Intution : Treat each cell as a node and form connected components of 1s using DSU.
+If we flip a 0 → 1, it can connect multiple adjacent components, so the new island size becomes the sum of distinct neighboring component sizes + 1.
+How to represent I,J in size , parent = I,J = I*n(lengthofcolumn)+J.
+Approch : 
+- Represent (i, j) as a node: node = i * n + j. 
+- Initialize DSU with n*n nodes.
+- For each cell with value 1: do union with all 4 adjacents and fill parent and size array . 
+- Initialize largestIsland .
+- Try flipping each 0
+- For every cell where grid[i][j] == 0:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Collect distinct ultimate parents of adjacent 1 cells using a HashSet. 
+Why ? suppose grid as - 
+11
+01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Sum their sizes:
+- newSize = 1 + sum(size[parent])
+- compare with largestIsland 
+Update maximum answer.</t>
+    </r>
+  </si>
+  <si>
+    <t>O(n^2 α(N^2))</t>
+  </si>
+  <si>
+    <t>1594. Maximum Non Negative Product in a Matrix</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/maximum-non-negative-product-in-a-matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intution: When traversing the grid to find the maximum product, we encounter a unique challenge that doesn't exist in "maximum sum" problems: Negative Numbers.
+A positive number multiplied by a large positive number stays large.
+A negative number multiplied by a very small negative number can become a very large positive number.
+Because of this "flip" property, we cannot simply keep track of the maximum product at each cell. We must also track the minimum product (the most negative value), as it has the potential to become the maximum product later if it encounters another negative integer.
+max[i][j] = best possible product from here
+min[i][j] = worst (most negative) product from here
+Approch : 
+- Use 2 dp table min and max .
+- intiliaze them with max and min values . 
+- at each steps - calculate max and min value by comparing with  down and right calls . 
+- return max[0][0] as answer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP </t>
+  </si>
+  <si>
+    <t>TC - O(M*N) - expoential (2^m+n) but as we are using memo - (m*n)</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/critical-connections-in-a-network</t>
+  </si>
+  <si>
+    <t>TC - O(V+E)
+SC - O(V)</t>
+  </si>
+  <si>
+    <t>Tarjan's Algorithm</t>
+  </si>
+  <si>
+    <t>1192. Critical Connections in a Network - Tarjan's Algorithm</t>
+  </si>
+  <si>
+    <t>INTUTION : If a child node can't reach any node visited before its parent . (i.e., no back-edge exists),
+then the edge connecting parent → child is a CRITICAL CONNECTION.
+APPROCH : 
+-  Maintain two arrays:
+  insertionTime[n], low[n]  // (minInsertionOfChildsCanReach)
+- Start DFS from any node.
+- Maintain a global timer (initially 1).
+- During DFS for a node:
+- Set:
+insertionTime[node] = low[node] = timer
+do - timer++
+- For each neighbor:
+- if neighbor == parent then continue;
+- If neighbor is not visited:
+-- Call DFS(neighbor, node)
+Update:
+low[node] = min(low[node], low[neighbor])
+- this tells us if we are visiting any previous node which is already visited if its visited will get low[neighbor]&lt;low[node].
+- After visiting a node completly
+- Check for bridge between:
+if (low[neighbor] &gt; insertionTime[node])
+→ edge (node, neighbor) is a bridge .</t>
+  </si>
+  <si>
+    <t>G-56. Articulation Point in Graph</t>
   </si>
 </sst>
 </file>
@@ -2613,9 +2756,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2629,6 +2769,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2991,6 +3134,147 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBB5AD9-6759-49B8-8C85-DCC62C1F65FC}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.6328125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.7265625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.90625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="19.26953125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.6328125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.54296875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.1796875" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="5" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="333.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="H2" s="5">
+        <v>3</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B3" s="6"/>
+      <c r="L3" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="8" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" s="8">
+        <v>3</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1" xr:uid="{2BBB5AD9-6759-49B8-8C85-DCC62C1F65FC}"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{78E200A1-F1DC-4FA8-ACD2-EB3A411CCC64}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{A45A0E55-7AB9-485C-AA0D-19E5272C99AD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9EF021-EC0E-48FF-9C7E-A5FF2E79A8F1}">
   <dimension ref="A1:L2"/>
@@ -3277,21 +3561,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627F4D11-A7C4-43BB-9B31-F105D2E4CA7B}">
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.90625" style="5" customWidth="1"/>
     <col min="2" max="2" width="43.26953125" style="5" customWidth="1"/>
     <col min="3" max="3" width="27.7265625" style="5" customWidth="1"/>
     <col min="4" max="4" width="26.26953125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.7265625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="17.6328125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="17.7265625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.6328125" style="8" customWidth="1"/>
     <col min="7" max="10" width="17.54296875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" style="8" customWidth="1"/>
     <col min="12" max="12" width="17.453125" style="5" customWidth="1"/>
     <col min="13" max="13" width="17.54296875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="17.6328125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="8.7265625" style="9"/>
+    <col min="14" max="14" width="17.6328125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="8.7265625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.35">
@@ -3310,7 +3594,7 @@
       <c r="E1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -3342,7 +3626,7 @@
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -3351,10 +3635,10 @@
       <c r="D2" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -3369,7 +3653,7 @@
       <c r="J2" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>49</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -3380,7 +3664,7 @@
       <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>137</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -3407,7 +3691,7 @@
       <c r="J3" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3415,19 +3699,19 @@
       <c r="A4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>148</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>33</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -3442,7 +3726,7 @@
       <c r="J4" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="8" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3450,7 +3734,7 @@
       <c r="A5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>146</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -3459,10 +3743,10 @@
       <c r="D5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -3474,7 +3758,7 @@
       <c r="I5" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>49</v>
       </c>
       <c r="M5" s="5" t="s">
@@ -3485,7 +3769,7 @@
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -3494,10 +3778,10 @@
       <c r="D6" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>33</v>
       </c>
       <c r="G6" s="5" t="s">
@@ -3509,7 +3793,7 @@
       <c r="I6" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>49</v>
       </c>
       <c r="M6" s="5" t="s">
@@ -3520,10 +3804,10 @@
       <c r="A7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>195</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -3555,10 +3839,10 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="232" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>62</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -3567,10 +3851,10 @@
       <c r="D8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="5" t="s">
@@ -3590,7 +3874,7 @@
       <c r="A9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>65</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -3599,10 +3883,10 @@
       <c r="D9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>66</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -3654,7 +3938,7 @@
       <c r="A11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -3663,10 +3947,10 @@
       <c r="D11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>60</v>
       </c>
       <c r="G11" s="5" t="s">
@@ -3695,10 +3979,10 @@
       <c r="D12" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="5" t="s">
@@ -3753,7 +4037,7 @@
       <c r="A14" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>98</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -3785,7 +4069,7 @@
       <c r="A15" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>102</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -3849,7 +4133,7 @@
       <c r="A17" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>120</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -3951,19 +4235,19 @@
       <c r="A20" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>152</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G20" s="5" t="s">
@@ -3975,7 +4259,7 @@
       <c r="I20" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L20" s="5" t="s">
@@ -3989,7 +4273,7 @@
       <c r="A21" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>157</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -3998,10 +4282,10 @@
       <c r="D21" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>138</v>
       </c>
       <c r="G21" s="5" t="s">
@@ -4010,7 +4294,7 @@
       <c r="H21" s="5">
         <v>4</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="K21" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L21" s="5" t="s">
@@ -4030,10 +4314,10 @@
       <c r="D22" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G22" s="5" t="s">
@@ -4042,7 +4326,7 @@
       <c r="H22" s="5">
         <v>4</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L22" s="5" t="s">
@@ -4056,19 +4340,19 @@
       <c r="A23" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>179</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G23" s="5" t="s">
@@ -4077,7 +4361,7 @@
       <c r="H23" s="5">
         <v>3</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K23" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L23" s="5" t="s">
@@ -4088,7 +4372,7 @@
       <c r="A24" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>177</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -4097,10 +4381,10 @@
       <c r="D24" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G24" s="5" t="s">
@@ -4109,7 +4393,7 @@
       <c r="H24" s="5">
         <v>3</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L24" s="5" t="s">
@@ -4120,7 +4404,7 @@
       <c r="A25" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>181</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -4129,10 +4413,10 @@
       <c r="D25" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G25" s="5" t="s">
@@ -4141,7 +4425,7 @@
       <c r="H25" s="5">
         <v>3</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="K25" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4149,7 +4433,7 @@
       <c r="A26" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>186</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -4158,10 +4442,10 @@
       <c r="D26" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G26" s="5" t="s">
@@ -4170,7 +4454,7 @@
       <c r="H26" s="5">
         <v>3</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L26" s="5" t="s">
@@ -4181,7 +4465,7 @@
       <c r="A27" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>191</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -4190,10 +4474,10 @@
       <c r="D27" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G27" s="5" t="s">
@@ -4205,7 +4489,7 @@
       <c r="I27" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L27" s="5" t="s">
@@ -4219,7 +4503,7 @@
       <c r="A28" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>201</v>
       </c>
       <c r="C28" s="5" t="s">
@@ -4228,10 +4512,10 @@
       <c r="D28" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="8" t="s">
         <v>203</v>
       </c>
       <c r="G28" s="5" t="s">
@@ -4243,7 +4527,7 @@
       <c r="I28" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L28" s="5" t="s">
@@ -4257,7 +4541,7 @@
       <c r="A29" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C29" s="5" t="s">
@@ -4266,10 +4550,10 @@
       <c r="D29" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>66</v>
       </c>
       <c r="G29" s="5" t="s">
@@ -4289,19 +4573,19 @@
       <c r="A30" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>227</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>43</v>
       </c>
       <c r="H30" s="5">
@@ -4315,7 +4599,7 @@
       <c r="A31" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>230</v>
       </c>
       <c r="C31" s="5" t="s">
@@ -4324,10 +4608,10 @@
       <c r="D31" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G31" s="5" t="s">
@@ -4353,7 +4637,7 @@
       <c r="D32" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="8" t="s">
         <v>244</v>
       </c>
       <c r="H32" s="5">
@@ -4376,10 +4660,10 @@
       <c r="D33" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G33" s="5" t="s">
@@ -4388,7 +4672,7 @@
       <c r="H33" s="5">
         <v>3</v>
       </c>
-      <c r="K33" s="9" t="s">
+      <c r="K33" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L33" s="5" t="s">
@@ -4402,7 +4686,7 @@
       <c r="A34" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>253</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -4411,10 +4695,10 @@
       <c r="D34" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G34" s="5" t="s">
@@ -4426,7 +4710,7 @@
       <c r="J34" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="K34" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4443,10 +4727,10 @@
       <c r="D35" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G35" s="5" t="s">
@@ -4458,7 +4742,7 @@
       <c r="J35" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="K35" s="9" t="s">
+      <c r="K35" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L35" s="5" t="s">
@@ -4476,16 +4760,16 @@
         <v>265</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>256</v>
@@ -4494,9 +4778,9 @@
         <v>3</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="K36" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="K36" s="8" t="s">
         <v>32</v>
       </c>
       <c r="L36" s="5" t="s">
@@ -4504,6 +4788,130 @@
       </c>
       <c r="M36" s="5" t="s">
         <v>254</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H37" s="5">
+        <v>3</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H38" s="5">
+        <v>3</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H39" s="5">
+        <v>3</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="C47" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4533,13 +4941,110 @@
     <hyperlink ref="B31" r:id="rId22" xr:uid="{3472C449-0813-4249-A912-7371C1132D75}"/>
     <hyperlink ref="B27" r:id="rId23" xr:uid="{E7B363CE-2ADD-4EB8-BDCC-4504C7B2FC63}"/>
     <hyperlink ref="B34" r:id="rId24" xr:uid="{878B70B8-85D8-488D-988D-D9EA1E0D237C}"/>
+    <hyperlink ref="B37" r:id="rId25" xr:uid="{B22C8E31-8548-4614-AF2C-D50B2AEDD07A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{520716B6-7F22-460B-B807-1EABD72CDD3C}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.54296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="26.08984375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.90625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="17.6328125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" style="5"/>
+    <col min="9" max="9" width="17.6328125" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" s="5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1" xr:uid="{520716B6-7F22-460B-B807-1EABD72CDD3C}"/>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{919D73E7-9EA6-43E1-B38C-FE27D065BFAD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD994AD9-DD9F-4AD2-9BE6-CF2C5785A85E}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4643,25 +5148,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D90093C-235B-4BFA-AC06-070A87C8F0C6}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.36328125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="40.36328125" style="8" customWidth="1"/>
     <col min="2" max="2" width="31" style="5" customWidth="1"/>
     <col min="3" max="3" width="28.36328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="16.36328125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="18.26953125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" style="9" customWidth="1"/>
-    <col min="7" max="7" width="19.26953125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="21.90625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="18.453125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="21.7265625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.54296875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="19.26953125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="21.90625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="21.7265625" style="8" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="17.453125" style="5" customWidth="1"/>
     <col min="13" max="13" width="17.26953125" style="5" customWidth="1"/>
-    <col min="14" max="14" width="17.36328125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="17.36328125" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
@@ -4680,7 +5185,7 @@
       <c r="E1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -4707,40 +5212,40 @@
       <c r="N1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="9"/>
+      <c r="O1" s="8"/>
     </row>
     <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>161</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>3</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="6" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4754,7 +5259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C97E19B9-CD82-4865-8D9B-AA4D0F508F84}">
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4763,11 +5268,11 @@
     <col min="2" max="2" width="17.90625" style="2" customWidth="1"/>
     <col min="3" max="3" width="26" style="5" customWidth="1"/>
     <col min="4" max="4" width="16.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.08984375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" style="8" customWidth="1"/>
     <col min="6" max="6" width="17.26953125" style="5" customWidth="1"/>
     <col min="7" max="7" width="16.36328125" customWidth="1"/>
-    <col min="8" max="8" width="21.26953125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" style="9"/>
+    <col min="8" max="8" width="21.26953125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="8.7265625" style="8"/>
     <col min="11" max="11" width="18.26953125" customWidth="1"/>
     <col min="12" max="12" width="17.26953125" customWidth="1"/>
   </cols>
@@ -4816,11 +5321,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="9" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" s="8" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>217</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -4829,25 +5334,25 @@
       <c r="D2" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>3</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4858,145 +5363,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBB5AD9-6759-49B8-8C85-DCC62C1F65FC}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="25.6328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="26.1796875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="25.7265625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.7265625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17.90625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="17.54296875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="19.26953125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.6328125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.54296875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17.1796875" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.7265625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="333.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="H2" s="5">
-        <v>3</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B3" s="7"/>
-      <c r="L3" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="9" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="H4" s="9">
-        <v>3</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>221</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:O1" xr:uid="{2BBB5AD9-6759-49B8-8C85-DCC62C1F65FC}"/>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{78E200A1-F1DC-4FA8-ACD2-EB3A411CCC64}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{A45A0E55-7AB9-485C-AA0D-19E5272C99AD}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DSA.xlsx
+++ b/DSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026\learninglog\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBAD9D4-9CC8-4F2A-A828-ABFD3FF1BD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557B80BC-4BA2-44CB-809C-232D6F0760F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="291">
   <si>
     <t xml:space="preserve">Problem Name </t>
   </si>
@@ -2615,7 +2615,13 @@
     <t>1192. Critical Connections in a Network - Tarjan's Algorithm</t>
   </si>
   <si>
-    <t>INTUTION : If a child node can't reach any node visited before its parent . (i.e., no back-edge exists),
+    <t>G-56. Articulation Point in Graph</t>
+  </si>
+  <si>
+    <t>https://github.com/satyam-learning-log/DSA/blob/master/DSA_TOPICS/Graph/Other_Algos_Graph/L1192_Bridge_In_Graph_OR_Critical_Connections_in_a_Network.java</t>
+  </si>
+  <si>
+    <t>INTUTION : If any child node can't reach any node visited before its parent . (i.e., no back-edge exists),
 then the edge connecting parent → child is a CRITICAL CONNECTION.
 APPROCH : 
 -  Maintain two arrays:
@@ -2639,7 +2645,113 @@
 → edge (node, neighbor) is a bridge .</t>
   </si>
   <si>
-    <t>G-56. Articulation Point in Graph</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notes :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Check the notebook - why its is different from bridges.
+MISTAKES : thought like it will solve If I count incoming edges of a vertex . Edge condtion what if - 1 - 2 , 1-3, 1-4 , 2-3, 3-4 .
+Bridge → edge removal disconnects
+Articulation → node removal disconnects
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPECIAL CASE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 
+Check why we need the boolean array to maintain articulation points . 
+If root has more than 1 child → articulation point
+    u
+   / \
+  v   x
+  |
+ (subtree)
+ u
+ |
+ v
+INTUTION :  We try to find nodes whose removal breaks the graph into multiple components. " not edge ". 
+APPROCH :
+- Build the graph:
+- Create the adjacency list using the given edges (if not already provided).
+- Initialize a variable timer (globally or pass it in DFS) to keep track of the discovery time of each node. 
+- The timer is usually initialized to 0 or 1.
+- Perform DFS for each component / starting from any node:
+- Start DFS for unvisited nodes.
+The starting node should have parent = -1.
+Inside DFS:
+Mark the current node as visited.
+Store:
+tin[node] → time of insertion (discovery time).
+low[node] → lowest reachable insertion time.
+Initialize a variable child = 0 to handle the special case for the starting node.
+Explore adjacent nodes:
+If the adjacent node is the parent: continue to the next node.
+If the adjacent node is not visited:
+Call DFS for this adjacent node (dfs(adjNode, node)).
+After returning from DFS, update → low[node] = min(low[node], low[adjNode]).
+Check articulation condition:
+If low[adjNode] ≥ tin[node] and parent != -1, then mark node as an articulation point.
+Increment child++.
+If the adjacent node is already visited: Update → low[node] = min(low[node], tin[adjNode]).
+Special case for the starting node:
+If parent == -1 and child &gt; 1, then mark this starting node as an articulation point.
+Result:
+After DFS completes, the answer (hash/boolean array) will store all articulation points.
+Important Note: While calculating low[], we do not consider the parent node or already visited nodes, as they themselves may be articulation points and could be removed.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4874,7 +4986,7 @@
         <v>283</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>284</v>
@@ -4904,9 +5016,42 @@
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>288</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
@@ -4942,9 +5087,10 @@
     <hyperlink ref="B27" r:id="rId23" xr:uid="{E7B363CE-2ADD-4EB8-BDCC-4504C7B2FC63}"/>
     <hyperlink ref="B34" r:id="rId24" xr:uid="{878B70B8-85D8-488D-988D-D9EA1E0D237C}"/>
     <hyperlink ref="B37" r:id="rId25" xr:uid="{B22C8E31-8548-4614-AF2C-D50B2AEDD07A}"/>
+    <hyperlink ref="B40" r:id="rId26" xr:uid="{E6671084-E393-42CA-8149-765DFA9CE219}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
 </worksheet>
 </file>
 
